--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC IV/LTAIPT_A63F04.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC IV/LTAIPT_A63F04.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1557" uniqueCount="729">
   <si>
     <t>48950</t>
   </si>
@@ -104,7 +104,7 @@
     <t>Denominación del área</t>
   </si>
   <si>
-    <t>Descripción breve y clara de cada objetivo institucional</t>
+    <t>Descripción breve y clara de cada objetivo institucional (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Indicadores y metas asociados a cada objetivo 
@@ -126,24 +126,531 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>E152096D03C9994AB68EBFBC5FD557B9</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>Subdirección de Planeación y Evaluación</t>
   </si>
   <si>
-    <t>proporcionar los insumos y materiales de higiene y saneamiento para garantizar la salud de los estudiantes y docentes de los TBC</t>
+    <t>Procesos académicos en beneficio de los estudiantes</t>
+  </si>
+  <si>
+    <t>6390049</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Planeaci%c3%b3n%20y%20Evaluaci%c3%b3n/</t>
+  </si>
+  <si>
+    <t>20/04/2023</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0C36898091745C7E6835C992F9FA10F9</t>
+  </si>
+  <si>
+    <t>Coadyuvar con pláticas y/o talleres para difundir la protección prevención y respeto de los derechos humanos la tolerancia la inclusión y la no discriminación entre la población</t>
+  </si>
+  <si>
+    <t>6390081</t>
+  </si>
+  <si>
+    <t>CE99B8155C7A4CB91E18F0EC66D618EB</t>
+  </si>
+  <si>
+    <t>Realizar talleres o pláticas para la prevención del delito</t>
+  </si>
+  <si>
+    <t>6390080</t>
+  </si>
+  <si>
+    <t>31A323CC47631035DFEEED1DCC0AB9D7</t>
+  </si>
+  <si>
+    <t>Capacitar actualizar y profesionalizar al personal docente</t>
+  </si>
+  <si>
+    <t>6390079</t>
+  </si>
+  <si>
+    <t>97144BA1F75F5E8158EEA25E3BC1239A</t>
+  </si>
+  <si>
+    <t>Realizar eventos deportivos y culturales</t>
+  </si>
+  <si>
+    <t>6390078</t>
+  </si>
+  <si>
+    <t>4B4C6FC57429A1B8B38CECF0A6085D34</t>
+  </si>
+  <si>
+    <t>Identificar a los estudiantes sobresalientes hombres para reconocer su esfuerzo con algún tipo de beca institucional</t>
+  </si>
+  <si>
+    <t>6390077</t>
+  </si>
+  <si>
+    <t>98763506097EADCD1B8ADA84223F2674</t>
+  </si>
+  <si>
+    <t>Identificar a las estudiantes sobresalientes mujeres para reconocer su esfuerzo con algún tipo de beca institucional</t>
+  </si>
+  <si>
+    <t>6390076</t>
+  </si>
+  <si>
+    <t>7A2E836F1800EB37A7F1CFC74C4BFE84</t>
+  </si>
+  <si>
+    <t>Difundir la oferta educativa de tbc en plataforma institucional y redes sociales mediante material impreso y digital</t>
+  </si>
+  <si>
+    <t>6390075</t>
+  </si>
+  <si>
+    <t>B6641E12475704EB408F3C2894D1BC69</t>
+  </si>
+  <si>
+    <t>Realizar el servicio de mantenimiento y en los diferentes planteles de telebachilleratos comunitarios</t>
+  </si>
+  <si>
+    <t>6390082</t>
+  </si>
+  <si>
+    <t>7F958D727981A3364A15D1A4131988B7</t>
+  </si>
+  <si>
+    <t>Lograr que los jóvenes permanezcan y concluyan sus estudios de nivel superior</t>
+  </si>
+  <si>
+    <t>6390048</t>
+  </si>
+  <si>
+    <t>C4F27E842C1FD3F547BCDFCB099334F8</t>
+  </si>
+  <si>
+    <t>Atender la demanda y acercar la oferta educativa de este nivel para asegurar la calidad de conocimientos en los jóvenes</t>
+  </si>
+  <si>
+    <t>6390047</t>
+  </si>
+  <si>
+    <t>D3A3CDDF884032090DBDCDF6BF2AF274</t>
+  </si>
+  <si>
+    <t>Difundir los códigos de ética y  de conducta en el Colegio</t>
+  </si>
+  <si>
+    <t>6390053</t>
+  </si>
+  <si>
+    <t>0E7A845AF0D9B1B78BA2369BA62E0611</t>
+  </si>
+  <si>
+    <t>Actualizar e implementar los planes y programas de estudio de acuerdo al modelo de la nueva escuela mexicana</t>
+  </si>
+  <si>
+    <t>6390052</t>
+  </si>
+  <si>
+    <t>AD3CEF2A0E417D4291080F5015092F34</t>
+  </si>
+  <si>
+    <t>Impartir conferencias sobre derechos humanos y equidad de género en planteles</t>
+  </si>
+  <si>
+    <t>6390051</t>
+  </si>
+  <si>
+    <t>B3230CEDFBD6BB2F0DD747A231F8B711</t>
+  </si>
+  <si>
+    <t>Mantenimiento y rehabilitación en planteles y áreas del colegio</t>
+  </si>
+  <si>
+    <t>6390050</t>
+  </si>
+  <si>
+    <t>614B3AC3679CF9AC151AC324EA738B0C</t>
+  </si>
+  <si>
+    <t>6390060</t>
+  </si>
+  <si>
+    <t>3DDC59333123E53596CA4A938AFA62C8</t>
+  </si>
+  <si>
+    <t>Implementar proyectos emprendedores en  planteles      EE COBACH</t>
+  </si>
+  <si>
+    <t>6390059</t>
+  </si>
+  <si>
+    <t>E340CFB01154617D033C1A1E1FEBB683</t>
+  </si>
+  <si>
+    <t>Aplicar el programa cátedras cobat en los 24 planteles</t>
+  </si>
+  <si>
+    <t>6390058</t>
+  </si>
+  <si>
+    <t>5B31B7EFC36D3BC47964C63E39C5FE0E</t>
+  </si>
+  <si>
+    <t>Identificar a los estudiantes sobresalientes para reconocer su esfuerzo con algún tipo de beca institucional para mujeres</t>
+  </si>
+  <si>
+    <t>6390057</t>
+  </si>
+  <si>
+    <t>28C7B46D03AABCD02CA259ACE6C026BF</t>
+  </si>
+  <si>
+    <t>Identificar a los estudiantes sobresalientes para reconocer su esfuerzo con algún tipo de beca institucional para hombres</t>
+  </si>
+  <si>
+    <t>6390056</t>
+  </si>
+  <si>
+    <t>9EFE6D1A891730735C329F7EE7620D81</t>
+  </si>
+  <si>
+    <t>Llevar a cabo eventos deportivos y culturales en el colegio</t>
+  </si>
+  <si>
+    <t>6390055</t>
+  </si>
+  <si>
+    <t>5F9A900D6DBE99FB53331C989D36EFA5</t>
+  </si>
+  <si>
+    <t>Difundir la oferta educativa de cobat en la plataforma institucional y redes sociales</t>
+  </si>
+  <si>
+    <t>6390054</t>
+  </si>
+  <si>
+    <t>4CAA600235B6C0D42B7A1F2A48D2EEBB</t>
+  </si>
+  <si>
+    <t>Realizar campañas digitales para difundir la protección prevención y respeto de los derechos humanos la tolerancia la inclusión y la no discriminación entre la población</t>
+  </si>
+  <si>
+    <t>6390067</t>
+  </si>
+  <si>
+    <t>A5F7E0342C3AF53F04F75EB02B62D39A</t>
+  </si>
+  <si>
+    <t>Establecer relaciones y convenios con instituciones educativas</t>
+  </si>
+  <si>
+    <t>6390066</t>
+  </si>
+  <si>
+    <t>5406AAB48E0C503EB9E627CB4B46F494</t>
+  </si>
+  <si>
+    <t>Organizar ferias de orientación educativa para los estudiantes</t>
+  </si>
+  <si>
+    <t>6390065</t>
+  </si>
+  <si>
+    <t>B3E3DB835C8184F43B8359A1E90AFB9D</t>
+  </si>
+  <si>
+    <t>Dar seguimiento a los trabajos coordinados entre itea y cobat</t>
+  </si>
+  <si>
+    <t>6390064</t>
+  </si>
+  <si>
+    <t>F4102D861094A5D6EED9A1099447B740</t>
+  </si>
+  <si>
+    <t>Realizar campañas para la prevención del delito</t>
+  </si>
+  <si>
+    <t>6390063</t>
+  </si>
+  <si>
+    <t>8EE614C15BE79EE49447D10D9F07DC84</t>
+  </si>
+  <si>
+    <t>Capacitar y actualizar al personal directivo administrativo y de apoyo del Colegio</t>
+  </si>
+  <si>
+    <t>6390062</t>
+  </si>
+  <si>
+    <t>6AE0E7987358317B6A9D5903AE674D18</t>
+  </si>
+  <si>
+    <t>Realizar conferencias con ponentes internacionales</t>
+  </si>
+  <si>
+    <t>6390061</t>
+  </si>
+  <si>
+    <t>A795241154C252CB98897D876A69F338</t>
+  </si>
+  <si>
+    <t>6390074</t>
+  </si>
+  <si>
+    <t>47C46D9E95C51E91ACC36A0FD95E82A9</t>
+  </si>
+  <si>
+    <t>Mantenimiento y rehabilitación en telebachilleratos comunitarios</t>
+  </si>
+  <si>
+    <t>6390073</t>
+  </si>
+  <si>
+    <t>16C24D05BC35FEDFBCD6C18C3E4869F1</t>
+  </si>
+  <si>
+    <t>Dar seguimiento a los procesos académicos que fortalezcan la modalidad de Telebachillerato Comunitario</t>
+  </si>
+  <si>
+    <t>6390072</t>
+  </si>
+  <si>
+    <t>CB73A236514BAA70128992E3C6172778</t>
+  </si>
+  <si>
+    <t>Lograr que los jóvenes concluyan sus estudios de nivel medio superior en la modalidad de Telebachillerato Comunitario</t>
+  </si>
+  <si>
+    <t>6390071</t>
+  </si>
+  <si>
+    <t>E6D6D93EE666B303992D8EDDFCAC9A46</t>
+  </si>
+  <si>
+    <t>6390070</t>
+  </si>
+  <si>
+    <t>56DCF9DBF25B616E46C2E7B11D21BB9C</t>
+  </si>
+  <si>
+    <t>Realizar mantenimiento técnico al equipo informático y de telecomunicaciones en planteles y  áreas administrativas</t>
+  </si>
+  <si>
+    <t>6390069</t>
+  </si>
+  <si>
+    <t>DAA1CA2545929738499F6662BF93C470</t>
+  </si>
+  <si>
+    <t>Realizar el servicio de mantenimiento y conservación de edificios en planteles dirección general y administrativa</t>
+  </si>
+  <si>
+    <t>6390068</t>
+  </si>
+  <si>
+    <t>Lograr que los jóvenes concluyan la educación media superior en el Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>2926532</t>
+  </si>
+  <si>
+    <t>Incrementar la eficiencia terminal en educación media superior en el estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>2926531</t>
+  </si>
+  <si>
+    <t>Implementar el programa cátedras COBAT de fomento a la lectura</t>
+  </si>
+  <si>
+    <t>2926537</t>
+  </si>
+  <si>
+    <t>Realizar campañas para el rescate de valores y prevención de problemáticas sociales</t>
+  </si>
+  <si>
+    <t>2926538</t>
+  </si>
+  <si>
+    <t>Implementar el Programa CONSTRUYE-T y actividades que fortalezcan el aspecto socioemocional en los estudiantes de los 24 planteles del Subsistema</t>
+  </si>
+  <si>
+    <t>2926536</t>
+  </si>
+  <si>
+    <t>Aplicar los Manuales del Programa Yo No Abandono en los 24 planteles</t>
+  </si>
+  <si>
+    <t>2926535</t>
+  </si>
+  <si>
+    <t>Atender las necesidades materiales del colegio</t>
+  </si>
+  <si>
+    <t>2926534</t>
+  </si>
+  <si>
+    <t>Dar seguimiento a los procesos académicos de los estudiantes</t>
+  </si>
+  <si>
+    <t>2926533</t>
+  </si>
+  <si>
+    <t>Realizar reportes de las asesorías académicas HFA para la regularización de los estudiantes</t>
+  </si>
+  <si>
+    <t>2926544</t>
+  </si>
+  <si>
+    <t>Capacitar, actualizar y profesionalizar al personal docente</t>
+  </si>
+  <si>
+    <t>2926543</t>
+  </si>
+  <si>
+    <t>2926542</t>
+  </si>
+  <si>
+    <t>Implementar actividades del programa ECOBACH de desarrollo sustentable</t>
+  </si>
+  <si>
+    <t>2926541</t>
+  </si>
+  <si>
+    <t>Organizar conferencias que promuevan la educación sexual y el respeto a la diversidad sexual desde el enfoque científico</t>
+  </si>
+  <si>
+    <t>2926540</t>
+  </si>
+  <si>
+    <t>Impartir conferencias sobre derechos humanos, equidad de género y trata de personas en planteles</t>
+  </si>
+  <si>
+    <t>2926539</t>
+  </si>
+  <si>
+    <t>Supervisar el seguimiento de la permanencia y promoción de los 24 planteles del Subsistema en el PC-SINEMS o su equivalente</t>
+  </si>
+  <si>
+    <t>2926549</t>
+  </si>
+  <si>
+    <t>Realizar y autorizar el estudio de equivalencia para estudiantes mujeres de los diferentes subsistemas que desean ingresar al colegio</t>
+  </si>
+  <si>
+    <t>2926550</t>
+  </si>
+  <si>
+    <t>Coordinar eventos culturales  del colegio</t>
+  </si>
+  <si>
+    <t>2926548</t>
+  </si>
+  <si>
+    <t>Coordinar eventos deportivos del colegio</t>
+  </si>
+  <si>
+    <t>2926547</t>
+  </si>
+  <si>
+    <t>2926546</t>
+  </si>
+  <si>
+    <t>Capacitar y actualizar al personal directivo, administrativo y de apoyo del colegio</t>
+  </si>
+  <si>
+    <t>2926545</t>
+  </si>
+  <si>
+    <t>Lograr la permanencia y conclusión de los estudiantes de educación media superior de la modalidad de telebachillerato comunitario</t>
+  </si>
+  <si>
+    <t>2926556</t>
+  </si>
+  <si>
+    <t>Proporcionar los insumos y materiales de higiene y saneamiento para garantizar la salud de los estudiantes y personal que integra el colegio</t>
+  </si>
+  <si>
+    <t>2926555</t>
+  </si>
+  <si>
+    <t>Atender las necesidades solicitadas para dar mantenimiento técnico al equipo informático</t>
+  </si>
+  <si>
+    <t>2926554</t>
+  </si>
+  <si>
+    <t>Realizar el servicio de mantenimiento y conservación de edificios en los diferentes planteles, así como en dirección general y áreas administrativas</t>
+  </si>
+  <si>
+    <t>2926553</t>
+  </si>
+  <si>
+    <t>Aplicar un programa de pruebas estandarizadas</t>
+  </si>
+  <si>
+    <t>2926552</t>
+  </si>
+  <si>
+    <t>Realizar y autorizar el estudio de equivalencia para estudiantes hombres de los diferentes subsistemas que desean ingresar al colegio</t>
+  </si>
+  <si>
+    <t>2926551</t>
+  </si>
+  <si>
+    <t>Realizar pláticas de prevención a problemáticas sociales a estudiantes mujeres</t>
+  </si>
+  <si>
+    <t>2926562</t>
+  </si>
+  <si>
+    <t>Impartir cursos de capacitación a los docentes</t>
+  </si>
+  <si>
+    <t>2926561</t>
+  </si>
+  <si>
+    <t>Construir antologías para los docentes y estudiantes de telebachillerato comunitario</t>
+  </si>
+  <si>
+    <t>2926560</t>
+  </si>
+  <si>
+    <t>Atender las necesidades de mantenimiento y reparación de los planteles</t>
+  </si>
+  <si>
+    <t>2926559</t>
+  </si>
+  <si>
+    <t>Dar seguimiento a los procesos académicos que fortalezcan la modalidad de telebachillerato comunitario</t>
+  </si>
+  <si>
+    <t>2926558</t>
+  </si>
+  <si>
+    <t>Disminuir el abandono escolar de los jovenes de educación media superior de la modalidad educativa telebachillerato comunitario</t>
+  </si>
+  <si>
+    <t>2926557</t>
   </si>
   <si>
     <t>2926568</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Subdireccion%20de%20Planeacion%20y%20Evaluacion/Calendarizacion%20de%20Metas%20Anual/METAS_COBAT_2022.pdf</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>Realizar trabajos de reparación y/o mantenimiento de inmuebles</t>
   </si>
   <si>
@@ -174,435 +681,120 @@
     <t>2926563</t>
   </si>
   <si>
-    <t>Realizar pláticas de prevención a problemáticas sociales a estudiantes mujeres</t>
-  </si>
-  <si>
-    <t>2926562</t>
-  </si>
-  <si>
-    <t>Impartir cursos de capacitación a los docentes</t>
-  </si>
-  <si>
-    <t>2926561</t>
-  </si>
-  <si>
-    <t>Construir antologías para los docentes y estudiantes de telebachillerato comunitario</t>
-  </si>
-  <si>
-    <t>2926560</t>
-  </si>
-  <si>
-    <t>Atender las necesidades de mantenimiento y reparación de los planteles</t>
-  </si>
-  <si>
-    <t>2926559</t>
-  </si>
-  <si>
-    <t>Dar seguimiento a los procesos académicos que fortalezcan la modalidad de telebachillerato comunitario</t>
-  </si>
-  <si>
-    <t>2926558</t>
-  </si>
-  <si>
-    <t>Disminuir el abandono escolar de los jovenes de educación media superior de la modalidad educativa telebachillerato comunitario</t>
-  </si>
-  <si>
-    <t>2926557</t>
-  </si>
-  <si>
-    <t>Lograr la permanencia y conclusión de los estudiantes de educación media superior de la modalidad de telebachillerato comunitario</t>
-  </si>
-  <si>
-    <t>2926556</t>
-  </si>
-  <si>
-    <t>Proporcionar los insumos y materiales de higiene y saneamiento para garantizar la salud de los estudiantes y personal que integra el colegio</t>
-  </si>
-  <si>
-    <t>2926555</t>
-  </si>
-  <si>
-    <t>Atender las necesidades solicitadas para dar mantenimiento técnico al equipo informático</t>
-  </si>
-  <si>
-    <t>2926554</t>
-  </si>
-  <si>
-    <t>Realizar el servicio de mantenimiento y conservación de edificios en los diferentes planteles, así como en dirección general y áreas administrativas</t>
-  </si>
-  <si>
-    <t>2926553</t>
-  </si>
-  <si>
-    <t>Aplicar un programa de pruebas estandarizadas</t>
-  </si>
-  <si>
-    <t>2926552</t>
-  </si>
-  <si>
-    <t>Realizar y autorizar el estudio de equivalencia para estudiantes hombres de los diferentes subsistemas que desean ingresar al colegio</t>
-  </si>
-  <si>
-    <t>2926551</t>
-  </si>
-  <si>
-    <t>Realizar y autorizar el estudio de equivalencia para estudiantes mujeres de los diferentes subsistemas que desean ingresar al colegio</t>
-  </si>
-  <si>
-    <t>2926550</t>
-  </si>
-  <si>
-    <t>Supervisar el seguimiento de la permanencia y promoción de los 24 planteles del Subsistema en el PC-SINEMS o su equivalente</t>
-  </si>
-  <si>
-    <t>2926549</t>
-  </si>
-  <si>
-    <t>Coordinar eventos culturales  del colegio</t>
-  </si>
-  <si>
-    <t>2926548</t>
-  </si>
-  <si>
-    <t>Coordinar eventos deportivos del colegio</t>
-  </si>
-  <si>
-    <t>2926547</t>
-  </si>
-  <si>
-    <t>Organizar ferias de orientación educativa para los estudiantes</t>
-  </si>
-  <si>
-    <t>2926546</t>
-  </si>
-  <si>
-    <t>Capacitar y actualizar al personal directivo, administrativo y de apoyo del colegio</t>
-  </si>
-  <si>
-    <t>2926545</t>
-  </si>
-  <si>
-    <t>Realizar reportes de las asesorías académicas HFA para la regularización de los estudiantes</t>
-  </si>
-  <si>
-    <t>2926544</t>
-  </si>
-  <si>
-    <t>Capacitar, actualizar y profesionalizar al personal docente</t>
-  </si>
-  <si>
-    <t>2926543</t>
-  </si>
-  <si>
-    <t>Realizar conferencias con ponentes internacionales</t>
-  </si>
-  <si>
-    <t>2926542</t>
-  </si>
-  <si>
-    <t>Implementar actividades del programa ECOBACH de desarrollo sustentable</t>
-  </si>
-  <si>
-    <t>2926541</t>
-  </si>
-  <si>
-    <t>Organizar conferencias que promuevan la educación sexual y el respeto a la diversidad sexual desde el enfoque científico</t>
-  </si>
-  <si>
-    <t>2926540</t>
-  </si>
-  <si>
-    <t>Impartir conferencias sobre derechos humanos, equidad de género y trata de personas en planteles</t>
-  </si>
-  <si>
-    <t>2926539</t>
-  </si>
-  <si>
-    <t>Realizar campañas para el rescate de valores y prevención de problemáticas sociales</t>
-  </si>
-  <si>
-    <t>2926538</t>
-  </si>
-  <si>
-    <t>Implementar el programa cátedras COBAT de fomento a la lectura</t>
-  </si>
-  <si>
-    <t>2926537</t>
-  </si>
-  <si>
-    <t>Implementar el Programa CONSTRUYE-T y actividades que fortalezcan el aspecto socioemocional en los estudiantes de los 24 planteles del Subsistema</t>
-  </si>
-  <si>
-    <t>2926536</t>
-  </si>
-  <si>
-    <t>Aplicar los Manuales del Programa Yo No Abandono en los 24 planteles</t>
-  </si>
-  <si>
-    <t>2926535</t>
-  </si>
-  <si>
-    <t>Atender las necesidades materiales del colegio</t>
-  </si>
-  <si>
-    <t>2926534</t>
-  </si>
-  <si>
-    <t>Dar seguimiento a los procesos académicos de los estudiantes</t>
-  </si>
-  <si>
-    <t>2926533</t>
-  </si>
-  <si>
-    <t>Lograr que los jóvenes concluyan la educación media superior en el Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>2926532</t>
-  </si>
-  <si>
-    <t>Incrementar la eficiencia terminal en educación media superior en el estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>2926531</t>
-  </si>
-  <si>
-    <t>212FEC406A17421B2611DF45618905C4</t>
-  </si>
-  <si>
-    <t>01/01/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
-  </si>
-  <si>
     <t>2645904</t>
   </si>
   <si>
-    <t>28/04/2022</t>
-  </si>
-  <si>
-    <t>9635CFFC34EC70C249CCC85F05801A9B</t>
+    <t>2645909</t>
+  </si>
+  <si>
+    <t>2645910</t>
+  </si>
+  <si>
+    <t>2645908</t>
+  </si>
+  <si>
+    <t>2645907</t>
+  </si>
+  <si>
+    <t>2645906</t>
+  </si>
+  <si>
+    <t>2645905</t>
+  </si>
+  <si>
+    <t>2645914</t>
+  </si>
+  <si>
+    <t>2645916</t>
+  </si>
+  <si>
+    <t>2645915</t>
+  </si>
+  <si>
+    <t>2645913</t>
+  </si>
+  <si>
+    <t>2645912</t>
+  </si>
+  <si>
+    <t>2645911</t>
+  </si>
+  <si>
+    <t>2645922</t>
+  </si>
+  <si>
+    <t>2645921</t>
+  </si>
+  <si>
+    <t>2645920</t>
+  </si>
+  <si>
+    <t>2645919</t>
+  </si>
+  <si>
+    <t>2645918</t>
+  </si>
+  <si>
+    <t>2645917</t>
+  </si>
+  <si>
+    <t>2645928</t>
+  </si>
+  <si>
+    <t>2645926</t>
+  </si>
+  <si>
+    <t>2645925</t>
+  </si>
+  <si>
+    <t>2645924</t>
+  </si>
+  <si>
+    <t>2645927</t>
+  </si>
+  <si>
+    <t>2645923</t>
+  </si>
+  <si>
+    <t>2645934</t>
+  </si>
+  <si>
+    <t>2645930</t>
+  </si>
+  <si>
+    <t>2645933</t>
+  </si>
+  <si>
+    <t>2645932</t>
+  </si>
+  <si>
+    <t>2645931</t>
+  </si>
+  <si>
+    <t>2645929</t>
+  </si>
+  <si>
+    <t>2645940</t>
+  </si>
+  <si>
+    <t>2645939</t>
+  </si>
+  <si>
+    <t>2645935</t>
+  </si>
+  <si>
+    <t>2645938</t>
+  </si>
+  <si>
+    <t>2645937</t>
+  </si>
+  <si>
+    <t>2645936</t>
   </si>
   <si>
     <t>2645941</t>
   </si>
   <si>
-    <t>FA0C0C6C3D3AC53C1766D363B8320D80</t>
-  </si>
-  <si>
-    <t>2645940</t>
-  </si>
-  <si>
-    <t>B58DFDA21341EE57CE8FE86D59E87F26</t>
-  </si>
-  <si>
-    <t>2645939</t>
-  </si>
-  <si>
-    <t>E7FB2A1587FC1492D6E7F46E62C64CEF</t>
-  </si>
-  <si>
-    <t>2645938</t>
-  </si>
-  <si>
-    <t>BD8785BB9F5856039CF81EA8F24E14D8</t>
-  </si>
-  <si>
-    <t>2645937</t>
-  </si>
-  <si>
-    <t>8A0930336BCA627E79E97B89A267C220</t>
-  </si>
-  <si>
-    <t>2645936</t>
-  </si>
-  <si>
-    <t>EB9B033402D038FF77C1215EAC9C8915</t>
-  </si>
-  <si>
-    <t>2645935</t>
-  </si>
-  <si>
-    <t>795974B9C698C3D9947732E3B109130B</t>
-  </si>
-  <si>
-    <t>2645934</t>
-  </si>
-  <si>
-    <t>3C25C8212DAA847C73C036EB644B9460</t>
-  </si>
-  <si>
-    <t>2645933</t>
-  </si>
-  <si>
-    <t>B60A54EBE8E38B2B3515333A71D76F85</t>
-  </si>
-  <si>
-    <t>2645932</t>
-  </si>
-  <si>
-    <t>7BC4054F741D55BFB63FD2946D77CF31</t>
-  </si>
-  <si>
-    <t>2645931</t>
-  </si>
-  <si>
-    <t>24563E390688F306CFABC102E2A2D7F8</t>
-  </si>
-  <si>
-    <t>2645930</t>
-  </si>
-  <si>
-    <t>87AECBB3BFFC1C49D5C532E2B01B04D4</t>
-  </si>
-  <si>
-    <t>2645929</t>
-  </si>
-  <si>
-    <t>D73D7262E5AE959D47DFED74D4D79819</t>
-  </si>
-  <si>
-    <t>2645928</t>
-  </si>
-  <si>
-    <t>B32B9E6E587F27CCEC8081A12C6D904B</t>
-  </si>
-  <si>
-    <t>2645927</t>
-  </si>
-  <si>
-    <t>06B47D02837AD63F1406A482623A421A</t>
-  </si>
-  <si>
-    <t>2645926</t>
-  </si>
-  <si>
-    <t>287AB757D8FD4A98134295C8C4CAA813</t>
-  </si>
-  <si>
-    <t>2645925</t>
-  </si>
-  <si>
-    <t>CBD62F60AE93F92D0902372EA0991044</t>
-  </si>
-  <si>
-    <t>2645924</t>
-  </si>
-  <si>
-    <t>8CDEE23D749DEC404D9470316DAD27C4</t>
-  </si>
-  <si>
-    <t>2645923</t>
-  </si>
-  <si>
-    <t>DB5B9E8DCE4A828DCCAAF248B10E3E25</t>
-  </si>
-  <si>
-    <t>2645922</t>
-  </si>
-  <si>
-    <t>A7EED5D0509F14939D1F0817F99D5AA7</t>
-  </si>
-  <si>
-    <t>2645921</t>
-  </si>
-  <si>
-    <t>B517C5CFB13B17CA54F7070A6CF5B133</t>
-  </si>
-  <si>
-    <t>2645920</t>
-  </si>
-  <si>
-    <t>2C2CF2CACAB628CC70CBB9670F8876F3</t>
-  </si>
-  <si>
-    <t>2645919</t>
-  </si>
-  <si>
-    <t>860B4E8DBF69A87D05B20D150AAECE06</t>
-  </si>
-  <si>
-    <t>2645918</t>
-  </si>
-  <si>
-    <t>0B03CCAB7BFEF651B67FB444F9F16E29</t>
-  </si>
-  <si>
-    <t>2645917</t>
-  </si>
-  <si>
-    <t>2643E01DFCF4C2BD323C4FFCE7A3C63C</t>
-  </si>
-  <si>
-    <t>2645916</t>
-  </si>
-  <si>
-    <t>F5B12FF69567DD3523ECC29624AC0BF7</t>
-  </si>
-  <si>
-    <t>2645915</t>
-  </si>
-  <si>
-    <t>8017D1A5A851E908E90C1C8BF839F6DF</t>
-  </si>
-  <si>
-    <t>2645914</t>
-  </si>
-  <si>
-    <t>2FD89DBD500C0819AD7DA3E97AFBF85F</t>
-  </si>
-  <si>
-    <t>2645913</t>
-  </si>
-  <si>
-    <t>C32982FBCBFEC11B1BC74EE8791E6BD6</t>
-  </si>
-  <si>
-    <t>2645912</t>
-  </si>
-  <si>
-    <t>C02E2BE482D51F9F9BDB1CE6460E69D9</t>
-  </si>
-  <si>
-    <t>2645911</t>
-  </si>
-  <si>
-    <t>8F8E543DAF3B9C208B266C7D2A8CFAE9</t>
-  </si>
-  <si>
-    <t>2645910</t>
-  </si>
-  <si>
-    <t>8D6F1E813A18F236A06AEFACA934E618</t>
-  </si>
-  <si>
-    <t>2645909</t>
-  </si>
-  <si>
-    <t>1195CB5BF328D76A16655E8AABE13B70</t>
-  </si>
-  <si>
-    <t>2645908</t>
-  </si>
-  <si>
-    <t>A6139EABA4ECA0553EDD88E0F3984EB1</t>
-  </si>
-  <si>
-    <t>2645907</t>
-  </si>
-  <si>
-    <t>B69A4CBE9D4BDE40A7558657D9EA648E</t>
-  </si>
-  <si>
-    <t>2645906</t>
-  </si>
-  <si>
-    <t>7B502F2B36212822F57D5BFCFB17A204</t>
-  </si>
-  <si>
-    <t>2645905</t>
-  </si>
-  <si>
     <t>Capacitar y actualizar al personal directivo, administrativo y de apoyo del colegio.</t>
   </si>
   <si>
@@ -1200,27 +1392,294 @@
     <t>Unidad de medida</t>
   </si>
   <si>
+    <t>4AFD16BD872D99834F929D24170821D7</t>
+  </si>
+  <si>
+    <t>Porcentaje</t>
+  </si>
+  <si>
+    <t>1D206C727E4C1097301F7F510DD5BA54</t>
+  </si>
+  <si>
+    <t>Taller</t>
+  </si>
+  <si>
+    <t>1D206C727E4C1097F1DC1DFDEDD3198E</t>
+  </si>
+  <si>
+    <t>Plática</t>
+  </si>
+  <si>
+    <t>1D206C727E4C1097D084CBEA26B3771A</t>
+  </si>
+  <si>
+    <t>Capacitación</t>
+  </si>
+  <si>
+    <t>1D206C727E4C10978AFE60E27A8B5708</t>
+  </si>
+  <si>
+    <t>Evento</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557C72C2D7B55E200735</t>
+  </si>
+  <si>
+    <t>Beca</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557CDF29A1C6B508E6FB</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557C8328B6562054C14A</t>
+  </si>
+  <si>
+    <t>Campaña</t>
+  </si>
+  <si>
+    <t>1D206C727E4C1097E53380C252CCC4D2</t>
+  </si>
+  <si>
+    <t>Área</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D9983DF3E9734D705ABC9</t>
+  </si>
+  <si>
+    <t>Estudiante</t>
+  </si>
+  <si>
+    <t>66DE5222A175D9BDD891280BAD23AD03</t>
+  </si>
+  <si>
+    <t>Tasa</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D998396B1AC61BBBAE634</t>
+  </si>
+  <si>
+    <t>Difusión</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D998339A109C30A137ED8</t>
+  </si>
+  <si>
+    <t>Plan de estudio</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D9983300CE53B2ADBB0CF</t>
+  </si>
+  <si>
+    <t>Conferencia</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D9983828B46A5CC1C4213</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC1385EF266F96AAFEE</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC1574A1B9EB99735E9</t>
+  </si>
+  <si>
+    <t>Proyecto</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC1AF263336138CB827</t>
+  </si>
+  <si>
+    <t>Cátedra</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D9983FAAE3565C3B9C0AA</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D9983E32E70B49760764F</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D998327832AA89F4A799C</t>
+  </si>
+  <si>
+    <t>4AFD16BD872D99831C153FD512667EEF</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC1543BACD093391CD9</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC17876383A505DFB41</t>
+  </si>
+  <si>
+    <t>Convenio</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC187F2D617264D1FBB</t>
+  </si>
+  <si>
+    <t>Feria</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC1D8371CDE7BB52AF7</t>
+  </si>
+  <si>
+    <t>Certificado</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC189FB867CE966CDE5</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC1D33938647EC0BA24</t>
+  </si>
+  <si>
+    <t>109389E725DD5AC1C05270503E1D5417</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557C18C1244529FEF0DF</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557C3C5813F4F0386416</t>
+  </si>
+  <si>
+    <t>Plantel</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557C519F61FF9B8780AA</t>
+  </si>
+  <si>
+    <t>Proceso</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557CED15C291E1FC3E1E</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557CF3E908F2B0CC639A</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557C06913B7058E3138D</t>
+  </si>
+  <si>
+    <t>8F45AB1DB1D6557CCD629D5849D70D36</t>
+  </si>
+  <si>
+    <t>D65B30A6D1FCF10647D7BDAEF7EBD6C1</t>
+  </si>
+  <si>
+    <t>A254FBAC4CBBFF6B3B2FCF5E97A865D0</t>
+  </si>
+  <si>
+    <t>BF4069094FB2DD9477BD6FC18FFDFA03</t>
+  </si>
+  <si>
+    <t>Reporte</t>
+  </si>
+  <si>
+    <t>719E3F0A875AE579C6274CCE64A2908C</t>
+  </si>
+  <si>
+    <t>AF0C6A63F4E1CE2D4AB83C441145691B</t>
+  </si>
+  <si>
+    <t>0A575F56799CE4656974A770BA03E0D9</t>
+  </si>
+  <si>
+    <t>012738C35D84500086C7588D8AF56FCB</t>
+  </si>
+  <si>
+    <t>A5E8D6F79EE89A425639D7CB0B2338D8</t>
+  </si>
+  <si>
+    <t>B6B21C6820DC9F26A12CAC2447F35552</t>
+  </si>
+  <si>
+    <t>E04F38AD96AC25529D4D70F6F38341BB</t>
+  </si>
+  <si>
+    <t>2ABDA6FC4F5468EA6BE51663779D4ED0</t>
+  </si>
+  <si>
+    <t>E660D39C92A4FF0216DEBE707C72CCC9</t>
+  </si>
+  <si>
+    <t>E48038C8CF6B0294CAD6F7403CE5E1C1</t>
+  </si>
+  <si>
+    <t>3FF41942D64EE6C60370ED0EC8B7E7D8</t>
+  </si>
+  <si>
+    <t>7B2BBF4170BE97EA36906611392252A0</t>
+  </si>
+  <si>
+    <t>09D6D8E16A12333851CB9993F47155D1</t>
+  </si>
+  <si>
+    <t>Equivalencia</t>
+  </si>
+  <si>
+    <t>681DAF9C51F99E6E8703FF9729286637</t>
+  </si>
+  <si>
+    <t>11BEE983AD2D7AEC34D12259181B65B0</t>
+  </si>
+  <si>
+    <t>B20656C4351209E92EA401147B434906</t>
+  </si>
+  <si>
+    <t>A71DCD660C3FF317D85B1D6946A6CADF</t>
+  </si>
+  <si>
+    <t>09CCDE4A22610427630C25B474A65C1A</t>
+  </si>
+  <si>
+    <t>8B3D3E204BF1705A8474D6BC1DF1EF6F</t>
+  </si>
+  <si>
+    <t>8E3974FF420D3E55E4145EC204C80AFD</t>
+  </si>
+  <si>
+    <t>1DB7FB5546B765C7C96ABBF2D2F53BB6</t>
+  </si>
+  <si>
+    <t>197B7678D66FD75BBD78A3FC79516F5D</t>
+  </si>
+  <si>
+    <t>Programa</t>
+  </si>
+  <si>
+    <t>F0C7D0F45DEAE04E2FD4A3B46C98504C</t>
+  </si>
+  <si>
+    <t>319035C07F2D0F8A688AE1EEBAEA5F8E</t>
+  </si>
+  <si>
+    <t>683B7420F0993C94E8821218A8652907</t>
+  </si>
+  <si>
+    <t>FF40225BE00D7DCD60A18294DD205BF3</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>D9114D9CA8844025838FC824EA953514</t>
+  </si>
+  <si>
+    <t>544528B926A6FE1D47CD181F620A64EF</t>
+  </si>
+  <si>
+    <t>5BB080ECB6FC3DD9DA70BDDEE721A33B</t>
+  </si>
+  <si>
     <t>D7FB46EA219BFCF98BAB47DF5F01BCF6</t>
   </si>
   <si>
-    <t>Porcentaje</t>
-  </si>
-  <si>
     <t>Proporcionar los insumos y materiales de higiene y saneamiento para garantizar la salud de los estudiantes y docentes de los TBC</t>
   </si>
   <si>
-    <t>Plantel</t>
-  </si>
-  <si>
     <t>689EE64ED5663E275D28CDCB0F5354C8</t>
   </si>
   <si>
     <t>D643B894F73A8B75F648C311DA7414A7</t>
   </si>
   <si>
-    <t>Reporte</t>
-  </si>
-  <si>
     <t>7B8C4596F49D300B627CA3DFF9EE6AEB</t>
   </si>
   <si>
@@ -1233,252 +1692,120 @@
     <t>8391A1F231B0DCC61ADB5F0E69E97A5B</t>
   </si>
   <si>
-    <t>Plática</t>
-  </si>
-  <si>
-    <t>319035C07F2D0F8A688AE1EEBAEA5F8E</t>
-  </si>
-  <si>
-    <t>683B7420F0993C94E8821218A8652907</t>
-  </si>
-  <si>
-    <t>Capacitación</t>
-  </si>
-  <si>
-    <t>FF40225BE00D7DCD60A18294DD205BF3</t>
-  </si>
-  <si>
-    <t>Documento</t>
-  </si>
-  <si>
-    <t>D9114D9CA8844025838FC824EA953514</t>
-  </si>
-  <si>
-    <t>544528B926A6FE1D47CD181F620A64EF</t>
-  </si>
-  <si>
-    <t>Proceso</t>
-  </si>
-  <si>
-    <t>5BB080ECB6FC3DD9DA70BDDEE721A33B</t>
-  </si>
-  <si>
-    <t>Estudiante</t>
-  </si>
-  <si>
-    <t>09CCDE4A22610427630C25B474A65C1A</t>
-  </si>
-  <si>
-    <t>8B3D3E204BF1705A8474D6BC1DF1EF6F</t>
-  </si>
-  <si>
-    <t>Área</t>
-  </si>
-  <si>
-    <t>8E3974FF420D3E55E4145EC204C80AFD</t>
-  </si>
-  <si>
-    <t>1DB7FB5546B765C7C96ABBF2D2F53BB6</t>
-  </si>
-  <si>
-    <t>197B7678D66FD75BBD78A3FC79516F5D</t>
-  </si>
-  <si>
-    <t>Programa</t>
-  </si>
-  <si>
-    <t>F0C7D0F45DEAE04E2FD4A3B46C98504C</t>
-  </si>
-  <si>
-    <t>Equivalencia</t>
-  </si>
-  <si>
-    <t>09D6D8E16A12333851CB9993F47155D1</t>
-  </si>
-  <si>
-    <t>7B2BBF4170BE97EA36906611392252A0</t>
-  </si>
-  <si>
-    <t>681DAF9C51F99E6E8703FF9729286637</t>
-  </si>
-  <si>
-    <t>Evento</t>
-  </si>
-  <si>
-    <t>11BEE983AD2D7AEC34D12259181B65B0</t>
-  </si>
-  <si>
-    <t>B20656C4351209E92EA401147B434906</t>
-  </si>
-  <si>
-    <t>A71DCD660C3FF317D85B1D6946A6CADF</t>
-  </si>
-  <si>
-    <t>B6B21C6820DC9F26A12CAC2447F35552</t>
-  </si>
-  <si>
-    <t>E04F38AD96AC25529D4D70F6F38341BB</t>
-  </si>
-  <si>
-    <t>2ABDA6FC4F5468EA6BE51663779D4ED0</t>
-  </si>
-  <si>
-    <t>Conferencia</t>
-  </si>
-  <si>
-    <t>E660D39C92A4FF0216DEBE707C72CCC9</t>
-  </si>
-  <si>
-    <t>E48038C8CF6B0294CAD6F7403CE5E1C1</t>
-  </si>
-  <si>
-    <t>3FF41942D64EE6C60370ED0EC8B7E7D8</t>
-  </si>
-  <si>
-    <t>719E3F0A875AE579C6274CCE64A2908C</t>
-  </si>
-  <si>
-    <t>Campaña</t>
-  </si>
-  <si>
-    <t>BF4069094FB2DD9477BD6FC18FFDFA03</t>
-  </si>
-  <si>
-    <t>AF0C6A63F4E1CE2D4AB83C441145691B</t>
-  </si>
-  <si>
-    <t>0A575F56799CE4656974A770BA03E0D9</t>
-  </si>
-  <si>
-    <t>012738C35D84500086C7588D8AF56FCB</t>
-  </si>
-  <si>
-    <t>A5E8D6F79EE89A425639D7CB0B2338D8</t>
-  </si>
-  <si>
-    <t>D65B30A6D1FCF10647D7BDAEF7EBD6C1</t>
-  </si>
-  <si>
-    <t>Certificado</t>
-  </si>
-  <si>
-    <t>A254FBAC4CBBFF6B3B2FCF5E97A865D0</t>
-  </si>
-  <si>
     <t>6D1F7BA9113DA61A21BBCB72C60C252C</t>
   </si>
   <si>
+    <t>657BEB8F74CFC804551E4D23711CBCD7</t>
+  </si>
+  <si>
+    <t>AA06E59966E5532CCFB25FE093659BE4</t>
+  </si>
+  <si>
+    <t>A32D0EA11B6080819514C1ADC59C8A4C</t>
+  </si>
+  <si>
+    <t>AE188F2E95FD9FC38B76928A4601CC6E</t>
+  </si>
+  <si>
+    <t>EE23D2023717F9BA9C7E3C4B54AA1346</t>
+  </si>
+  <si>
+    <t>772E33FEA0DCD7CF72C4D7A712443E59</t>
+  </si>
+  <si>
+    <t>75BCF36B5A73ED84AB7FF47E352A76F5</t>
+  </si>
+  <si>
+    <t>1CA2728980316601181B026721857A9D</t>
+  </si>
+  <si>
+    <t>4509C8DF033528AE1852D73473D0BF81</t>
+  </si>
+  <si>
+    <t>24F65FF89273328145DB4AA34C3520ED</t>
+  </si>
+  <si>
+    <t>B4BF732AA5FEA065B10A16FF186EA405</t>
+  </si>
+  <si>
+    <t>C0E7D23E99CA5F128BA4D925722D0977</t>
+  </si>
+  <si>
+    <t>AA42099C4EE2C56BFFA001757CF209A2</t>
+  </si>
+  <si>
+    <t>C62C8596E612925785C6F27FC6C82E1F</t>
+  </si>
+  <si>
+    <t>CA34F1B661DBD8C3657C49C67AE0F3DA</t>
+  </si>
+  <si>
+    <t>B7AFA18B6AC5363680884808D957445B</t>
+  </si>
+  <si>
+    <t>1AF7A2CE270F8415F4CEA089DE3129CC</t>
+  </si>
+  <si>
+    <t>DBFDB04066E1EE1ED6A0142E96B11E8E</t>
+  </si>
+  <si>
+    <t>83FEA3D7E34949C4B81B8E1EF6FC6E8B</t>
+  </si>
+  <si>
+    <t>42F9D0CB9AF21DE43303F6C5AB212A19</t>
+  </si>
+  <si>
+    <t>4826AB9C044E7CB42CEA3CEA80B809AB</t>
+  </si>
+  <si>
+    <t>A0C4DB30C8CF7C4962312875512830B7</t>
+  </si>
+  <si>
+    <t>3BBC92BF0F510A7C3F1C241C454C4CFE</t>
+  </si>
+  <si>
+    <t>4D99FBCF9C0EC0349A835905403BF690</t>
+  </si>
+  <si>
+    <t>FADD965CFB39E3D587E8718B12023351</t>
+  </si>
+  <si>
+    <t>8470E56923747B8F5D38E4648D24E54B</t>
+  </si>
+  <si>
+    <t>CDAF06C798B05E338D5A572555B7E04E</t>
+  </si>
+  <si>
+    <t>8CC53DF33E6C04020B643F050FDEA08A</t>
+  </si>
+  <si>
+    <t>723444C106B9C395A1962DE4EDC342FB</t>
+  </si>
+  <si>
+    <t>674A94E2DCBE2FE18E3F0FF168C485B4</t>
+  </si>
+  <si>
+    <t>E4989386CEC49030824C2F46359CF10F</t>
+  </si>
+  <si>
+    <t>801CDFC94BACAE311BF1F485E5D8B3C9</t>
+  </si>
+  <si>
+    <t>DC558D65576C8788131DD1CDD63463BF</t>
+  </si>
+  <si>
+    <t>CFD2F24980D6050B72058007D8301226</t>
+  </si>
+  <si>
+    <t>EE3C71C7E34AFCE4E70F7FDCA8DAA393</t>
+  </si>
+  <si>
+    <t>4CE7FEC4E22D7CBE7D888C1A9EEB6C8F</t>
+  </si>
+  <si>
     <t>210488B9E66CE8688A4FC12F940AF1AB</t>
   </si>
   <si>
-    <t>E4989386CEC49030824C2F46359CF10F</t>
-  </si>
-  <si>
-    <t>801CDFC94BACAE311BF1F485E5D8B3C9</t>
-  </si>
-  <si>
-    <t>CFD2F24980D6050B72058007D8301226</t>
-  </si>
-  <si>
-    <t>EE3C71C7E34AFCE4E70F7FDCA8DAA393</t>
-  </si>
-  <si>
-    <t>4CE7FEC4E22D7CBE7D888C1A9EEB6C8F</t>
-  </si>
-  <si>
-    <t>DC558D65576C8788131DD1CDD63463BF</t>
-  </si>
-  <si>
-    <t>FADD965CFB39E3D587E8718B12023351</t>
-  </si>
-  <si>
-    <t>CDAF06C798B05E338D5A572555B7E04E</t>
-  </si>
-  <si>
-    <t>8CC53DF33E6C04020B643F050FDEA08A</t>
-  </si>
-  <si>
-    <t>723444C106B9C395A1962DE4EDC342FB</t>
-  </si>
-  <si>
-    <t>8470E56923747B8F5D38E4648D24E54B</t>
-  </si>
-  <si>
-    <t>674A94E2DCBE2FE18E3F0FF168C485B4</t>
-  </si>
-  <si>
-    <t>83FEA3D7E34949C4B81B8E1EF6FC6E8B</t>
-  </si>
-  <si>
-    <t>3BBC92BF0F510A7C3F1C241C454C4CFE</t>
-  </si>
-  <si>
-    <t>42F9D0CB9AF21DE43303F6C5AB212A19</t>
-  </si>
-  <si>
-    <t>4826AB9C044E7CB42CEA3CEA80B809AB</t>
-  </si>
-  <si>
-    <t>A0C4DB30C8CF7C4962312875512830B7</t>
-  </si>
-  <si>
-    <t>4D99FBCF9C0EC0349A835905403BF690</t>
-  </si>
-  <si>
-    <t>AA42099C4EE2C56BFFA001757CF209A2</t>
-  </si>
-  <si>
-    <t>C62C8596E612925785C6F27FC6C82E1F</t>
-  </si>
-  <si>
-    <t>CA34F1B661DBD8C3657C49C67AE0F3DA</t>
-  </si>
-  <si>
-    <t>B7AFA18B6AC5363680884808D957445B</t>
-  </si>
-  <si>
-    <t>1AF7A2CE270F8415F4CEA089DE3129CC</t>
-  </si>
-  <si>
-    <t>DBFDB04066E1EE1ED6A0142E96B11E8E</t>
-  </si>
-  <si>
-    <t>1CA2728980316601181B026721857A9D</t>
-  </si>
-  <si>
-    <t>4509C8DF033528AE1852D73473D0BF81</t>
-  </si>
-  <si>
-    <t>75BCF36B5A73ED84AB7FF47E352A76F5</t>
-  </si>
-  <si>
-    <t>24F65FF89273328145DB4AA34C3520ED</t>
-  </si>
-  <si>
-    <t>B4BF732AA5FEA065B10A16FF186EA405</t>
-  </si>
-  <si>
-    <t>C0E7D23E99CA5F128BA4D925722D0977</t>
-  </si>
-  <si>
-    <t>AA06E59966E5532CCFB25FE093659BE4</t>
-  </si>
-  <si>
-    <t>657BEB8F74CFC804551E4D23711CBCD7</t>
-  </si>
-  <si>
-    <t>A32D0EA11B6080819514C1ADC59C8A4C</t>
-  </si>
-  <si>
-    <t>AE188F2E95FD9FC38B76928A4601CC6E</t>
-  </si>
-  <si>
-    <t>EE23D2023717F9BA9C7E3C4B54AA1346</t>
-  </si>
-  <si>
-    <t>772E33FEA0DCD7CF72C4D7A712443E59</t>
-  </si>
-  <si>
     <t>3D8754BD2BF1330AAA67158C89720D94</t>
   </si>
   <si>
@@ -1738,9 +2065,6 @@
   </si>
   <si>
     <t>A861196B6CB7318E6477BD49F9E6CBD4</t>
-  </si>
-  <si>
-    <t>Taller</t>
   </si>
   <si>
     <t>5204ED5BE85FF6D7DA54AE35675B8E6D</t>
@@ -2274,7 +2598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
@@ -2451,1446 +2775,1370 @@
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>114</v>
+        <v>41</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>121</v>
+        <v>46</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J9" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="K11" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>129</v>
+        <v>58</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>131</v>
+        <v>61</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>135</v>
+        <v>67</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J21" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J22" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J23" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>93</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>155</v>
+        <v>96</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>156</v>
+        <v>98</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J26" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I28" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J30" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J31" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>168</v>
+        <v>116</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J32" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J33" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>171</v>
+        <v>120</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="H34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J34" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J35" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>176</v>
+        <v>128</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="H37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I37" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J37" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J38" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="H39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I39" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J39" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="H40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I40" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J40" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>186</v>
+        <v>141</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J41" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="H42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J42" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>117</v>
+        <v>38</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="H43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="J43" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3909,13 +4157,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E218"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="127.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="148.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3932,3071 +4180,3683 @@
     </row>
     <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>387</v>
+        <v>451</v>
       </c>
       <c r="D2" t="s">
-        <v>388</v>
+        <v>452</v>
       </c>
       <c r="E2" t="s">
-        <v>389</v>
+        <v>453</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>390</v>
+        <v>454</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>391</v>
+        <v>455</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>392</v>
+        <v>456</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>393</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>394</v>
+        <v>458</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>396</v>
+        <v>41</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>397</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>398</v>
+        <v>460</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>397</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>399</v>
+        <v>462</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>400</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>401</v>
+        <v>464</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>402</v>
+        <v>466</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>403</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>404</v>
+        <v>468</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>405</v>
+        <v>469</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>406</v>
+        <v>470</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>405</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>407</v>
+        <v>471</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>408</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>409</v>
+        <v>473</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>410</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>411</v>
+        <v>475</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>397</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>412</v>
+        <v>477</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>413</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>414</v>
+        <v>479</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>415</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>416</v>
+        <v>481</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>415</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>417</v>
+        <v>483</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>418</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>419</v>
+        <v>485</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>397</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>420</v>
+        <v>486</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>418</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>421</v>
+        <v>487</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>422</v>
+        <v>488</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>423</v>
+        <v>489</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>424</v>
+        <v>490</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>425</v>
+        <v>491</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>424</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>426</v>
+        <v>492</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>400</v>
+        <v>469</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>428</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>429</v>
+        <v>494</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>428</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>430</v>
+        <v>495</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>428</v>
+        <v>472</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>431</v>
+        <v>496</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>408</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>432</v>
+        <v>498</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>88</v>
+        <v>115</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>400</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>433</v>
+        <v>500</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>408</v>
+        <v>501</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>434</v>
+        <v>502</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>436</v>
+        <v>503</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>437</v>
+        <v>504</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>438</v>
+        <v>505</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>439</v>
+        <v>506</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>440</v>
+        <v>507</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>441</v>
+        <v>508</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>400</v>
+        <v>509</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>442</v>
+        <v>510</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>400</v>
+        <v>501</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>443</v>
+        <v>511</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>400</v>
+        <v>478</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>444</v>
+        <v>512</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>418</v>
+        <v>474</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>445</v>
+        <v>513</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>413</v>
+        <v>474</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>446</v>
+        <v>514</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>447</v>
+        <v>501</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>447</v>
+        <v>501</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>448</v>
+        <v>515</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>449</v>
+        <v>516</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>395</v>
+        <v>517</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>450</v>
+        <v>518</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>396</v>
+        <v>154</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>397</v>
+        <v>472</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>451</v>
+        <v>519</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>397</v>
+        <v>517</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>452</v>
+        <v>520</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>400</v>
+        <v>517</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>128</v>
+        <v>161</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>453</v>
+        <v>521</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>400</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>454</v>
+        <v>522</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>48</v>
+        <v>162</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>403</v>
+        <v>509</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>455</v>
+        <v>523</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>405</v>
+        <v>517</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>456</v>
+        <v>524</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>52</v>
+        <v>166</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>405</v>
+        <v>465</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>457</v>
+        <v>525</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>408</v>
+        <v>484</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>458</v>
+        <v>526</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>410</v>
+        <v>517</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>459</v>
+        <v>527</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>58</v>
+        <v>171</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>397</v>
+        <v>484</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>460</v>
+        <v>528</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>413</v>
+        <v>484</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>461</v>
+        <v>529</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>415</v>
+        <v>517</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>462</v>
+        <v>530</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>64</v>
+        <v>177</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>415</v>
+        <v>531</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>463</v>
+        <v>532</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>464</v>
+        <v>533</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>397</v>
+        <v>467</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>465</v>
+        <v>534</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>418</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>466</v>
+        <v>535</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>72</v>
+        <v>184</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>422</v>
+        <v>465</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>467</v>
+        <v>536</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>74</v>
+        <v>186</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>424</v>
+        <v>476</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>468</v>
+        <v>537</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>469</v>
+        <v>538</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>400</v>
+        <v>507</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>470</v>
+        <v>539</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>428</v>
+        <v>474</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>471</v>
+        <v>540</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>82</v>
+        <v>194</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>428</v>
+        <v>541</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>472</v>
+        <v>542</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>428</v>
+        <v>531</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>473</v>
+        <v>543</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>86</v>
+        <v>198</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>408</v>
+        <v>463</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>474</v>
+        <v>544</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>400</v>
+        <v>465</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>475</v>
+        <v>545</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>408</v>
+        <v>546</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>476</v>
+        <v>547</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>92</v>
+        <v>204</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>435</v>
+        <v>507</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>477</v>
+        <v>548</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>400</v>
+        <v>509</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>478</v>
+        <v>549</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>96</v>
+        <v>208</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>435</v>
+        <v>476</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>479</v>
+        <v>550</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>98</v>
+        <v>551</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>435</v>
+        <v>507</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>480</v>
+        <v>552</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>100</v>
+        <v>211</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>440</v>
+        <v>507</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>481</v>
+        <v>553</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>102</v>
+        <v>213</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>400</v>
+        <v>517</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>482</v>
+        <v>554</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>104</v>
+        <v>215</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>400</v>
+        <v>517</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>483</v>
+        <v>555</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>400</v>
+        <v>556</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>484</v>
+        <v>557</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>485</v>
+        <v>558</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>395</v>
+        <v>459</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>413</v>
+        <v>459</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>486</v>
+        <v>559</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>447</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>284</v>
+        <v>223</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>487</v>
+        <v>560</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>232</v>
+        <v>152</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>488</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>285</v>
+        <v>224</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>489</v>
+        <v>561</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>233</v>
+        <v>158</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>286</v>
+        <v>225</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>491</v>
+        <v>562</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>492</v>
+        <v>459</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>287</v>
+        <v>226</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>493</v>
+        <v>563</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>288</v>
+        <v>227</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>494</v>
+        <v>564</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>236</v>
+        <v>148</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>496</v>
+        <v>565</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>497</v>
+        <v>459</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>237</v>
+        <v>169</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>497</v>
+        <v>517</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>498</v>
+        <v>566</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>499</v>
+        <v>459</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>238</v>
+        <v>166</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>499</v>
+        <v>465</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>500</v>
+        <v>567</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>499</v>
+        <v>459</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>239</v>
+        <v>127</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>501</v>
+        <v>568</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>502</v>
+        <v>459</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>293</v>
+        <v>232</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>503</v>
+        <v>569</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>294</v>
+        <v>233</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>504</v>
+        <v>570</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>242</v>
+        <v>154</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>505</v>
+        <v>472</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>295</v>
+        <v>234</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>506</v>
+        <v>571</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>507</v>
+        <v>459</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>508</v>
+        <v>572</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>509</v>
+        <v>459</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>244</v>
+        <v>179</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>509</v>
+        <v>467</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>297</v>
+        <v>236</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>510</v>
+        <v>573</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>511</v>
+        <v>574</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>512</v>
+        <v>459</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>246</v>
+        <v>115</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>512</v>
+        <v>467</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>299</v>
+        <v>238</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>513</v>
+        <v>575</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>514</v>
+        <v>459</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>247</v>
+        <v>184</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>514</v>
+        <v>465</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>515</v>
+        <v>576</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>516</v>
+        <v>459</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>248</v>
+        <v>164</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>301</v>
+        <v>240</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>517</v>
+        <v>577</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>516</v>
+        <v>459</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>249</v>
+        <v>188</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>516</v>
+        <v>474</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>302</v>
+        <v>241</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>518</v>
+        <v>578</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>502</v>
+        <v>459</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>303</v>
+        <v>242</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>519</v>
+        <v>579</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>520</v>
+        <v>459</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>304</v>
+        <v>243</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>521</v>
+        <v>580</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>520</v>
+        <v>459</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>522</v>
+        <v>581</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>520</v>
+        <v>459</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>306</v>
+        <v>245</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>523</v>
+        <v>582</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>524</v>
+        <v>459</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>254</v>
+        <v>177</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>307</v>
+        <v>246</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>525</v>
+        <v>583</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>255</v>
+        <v>200</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>308</v>
+        <v>247</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>526</v>
+        <v>584</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>524</v>
+        <v>476</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>524</v>
+        <v>476</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>309</v>
+        <v>248</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>527</v>
+        <v>585</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>528</v>
+        <v>459</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>257</v>
+        <v>202</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>310</v>
+        <v>249</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>529</v>
+        <v>586</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>258</v>
+        <v>204</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>311</v>
+        <v>250</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>530</v>
+        <v>587</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>528</v>
+        <v>459</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>259</v>
+        <v>206</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>531</v>
+        <v>588</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>532</v>
+        <v>476</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>260</v>
+        <v>186</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>532</v>
+        <v>476</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>313</v>
+        <v>252</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>533</v>
+        <v>589</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>534</v>
+        <v>459</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>261</v>
+        <v>211</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>534</v>
+        <v>507</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>314</v>
+        <v>253</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>535</v>
+        <v>590</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>315</v>
+        <v>254</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>536</v>
+        <v>591</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>263</v>
+        <v>198</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>490</v>
+        <v>463</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>537</v>
+        <v>592</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>490</v>
+        <v>459</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>317</v>
+        <v>256</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>538</v>
+        <v>593</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>512</v>
+        <v>459</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>512</v>
+        <v>556</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>318</v>
+        <v>257</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>539</v>
+        <v>594</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>505</v>
+        <v>463</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>319</v>
+        <v>258</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>540</v>
+        <v>595</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>509</v>
+        <v>459</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>266</v>
+        <v>551</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>320</v>
+        <v>348</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>541</v>
+        <v>596</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>542</v>
+        <v>597</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>542</v>
+        <v>597</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>543</v>
+        <v>598</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>397</v>
+        <v>599</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>42</v>
+        <v>297</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>397</v>
+        <v>599</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>322</v>
+        <v>350</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>400</v>
+        <v>601</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>94</v>
+        <v>298</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>400</v>
+        <v>601</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>545</v>
+        <v>602</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>546</v>
+        <v>599</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>547</v>
+        <v>603</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>400</v>
+        <v>604</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>400</v>
+        <v>604</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>548</v>
+        <v>605</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>403</v>
+        <v>606</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>48</v>
+        <v>301</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>403</v>
+        <v>606</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>549</v>
+        <v>607</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>405</v>
+        <v>608</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>405</v>
+        <v>608</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>550</v>
+        <v>609</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>551</v>
+        <v>608</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>551</v>
+        <v>608</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>328</v>
+        <v>356</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>552</v>
+        <v>610</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>551</v>
+        <v>611</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>271</v>
+        <v>304</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>551</v>
+        <v>611</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>553</v>
+        <v>612</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>410</v>
+        <v>597</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>410</v>
+        <v>597</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>554</v>
+        <v>613</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>397</v>
+        <v>614</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>273</v>
+        <v>306</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>397</v>
+        <v>614</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>555</v>
+        <v>615</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>413</v>
+        <v>616</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>274</v>
+        <v>307</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>413</v>
+        <v>616</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>332</v>
+        <v>360</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>556</v>
+        <v>617</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>415</v>
+        <v>618</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>415</v>
+        <v>618</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>557</v>
+        <v>619</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>447</v>
+        <v>597</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>447</v>
+        <v>597</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>558</v>
+        <v>620</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>397</v>
+        <v>621</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>397</v>
+        <v>621</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>335</v>
+        <v>363</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>559</v>
+        <v>622</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>418</v>
+        <v>623</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>217</v>
+        <v>311</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>418</v>
+        <v>623</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>336</v>
+        <v>364</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>560</v>
+        <v>624</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>422</v>
+        <v>625</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>278</v>
+        <v>312</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>422</v>
+        <v>625</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>561</v>
+        <v>626</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>424</v>
+        <v>625</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>279</v>
+        <v>313</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>424</v>
+        <v>625</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>562</v>
+        <v>627</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>424</v>
+        <v>611</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>424</v>
+        <v>611</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>563</v>
+        <v>628</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>410</v>
+        <v>629</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>280</v>
+        <v>315</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>410</v>
+        <v>629</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>564</v>
+        <v>630</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>428</v>
+        <v>629</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>281</v>
+        <v>316</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>428</v>
+        <v>629</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>341</v>
+        <v>369</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>565</v>
+        <v>631</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>428</v>
+        <v>629</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>282</v>
+        <v>317</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>428</v>
+        <v>629</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>566</v>
+        <v>632</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>428</v>
+        <v>633</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>428</v>
+        <v>633</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>567</v>
+        <v>634</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>408</v>
+        <v>599</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>195</v>
+        <v>319</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>408</v>
+        <v>599</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>344</v>
+        <v>372</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>568</v>
+        <v>635</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>400</v>
+        <v>633</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>196</v>
+        <v>320</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>400</v>
+        <v>633</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>569</v>
+        <v>636</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>408</v>
+        <v>637</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>197</v>
+        <v>321</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>408</v>
+        <v>637</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>346</v>
+        <v>374</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>570</v>
+        <v>638</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>435</v>
+        <v>599</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>198</v>
+        <v>322</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>435</v>
+        <v>599</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>571</v>
+        <v>639</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>400</v>
+        <v>637</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>94</v>
+        <v>323</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>400</v>
+        <v>637</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>572</v>
+        <v>640</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>435</v>
+        <v>641</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>199</v>
+        <v>324</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>435</v>
+        <v>641</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>573</v>
+        <v>642</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>574</v>
+        <v>643</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>350</v>
+        <v>378</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>575</v>
+        <v>644</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>440</v>
+        <v>599</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>440</v>
+        <v>599</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>351</v>
+        <v>379</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>576</v>
+        <v>645</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>400</v>
+        <v>599</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>202</v>
+        <v>327</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>400</v>
+        <v>599</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>352</v>
+        <v>380</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>577</v>
+        <v>646</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>400</v>
+        <v>599</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>203</v>
+        <v>328</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>400</v>
+        <v>599</v>
       </c>
     </row>
     <row r="149" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>578</v>
+        <v>647</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>400</v>
+        <v>621</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>204</v>
+        <v>329</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>400</v>
+        <v>621</v>
       </c>
     </row>
     <row r="150" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>354</v>
+        <v>382</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>579</v>
+        <v>648</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>418</v>
+        <v>614</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>205</v>
+        <v>306</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>418</v>
+        <v>614</v>
       </c>
     </row>
     <row r="151" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>580</v>
+        <v>649</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>413</v>
+        <v>618</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>206</v>
+        <v>330</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>413</v>
+        <v>618</v>
       </c>
     </row>
     <row r="152" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>356</v>
+        <v>384</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>581</v>
+        <v>650</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>447</v>
+        <v>651</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>207</v>
+        <v>331</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>447</v>
+        <v>651</v>
       </c>
     </row>
     <row r="153" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>357</v>
+        <v>385</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>582</v>
+        <v>652</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>395</v>
+        <v>507</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>395</v>
+        <v>507</v>
       </c>
     </row>
     <row r="154" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>358</v>
+        <v>386</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>583</v>
+        <v>653</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>395</v>
+        <v>517</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>397</v>
+        <v>517</v>
       </c>
     </row>
     <row r="155" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>359</v>
+        <v>387</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>585</v>
+        <v>655</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>586</v>
+        <v>332</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>415</v>
+        <v>655</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>587</v>
+        <v>656</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>395</v>
+        <v>517</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>210</v>
+        <v>333</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>400</v>
+        <v>517</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>361</v>
+        <v>389</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>588</v>
+        <v>657</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>395</v>
+        <v>556</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>403</v>
+        <v>556</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>362</v>
+        <v>390</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>589</v>
+        <v>658</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>395</v>
+        <v>463</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>212</v>
+        <v>334</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>408</v>
+        <v>463</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>590</v>
+        <v>659</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>395</v>
+        <v>660</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>213</v>
+        <v>335</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>422</v>
+        <v>660</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>591</v>
+        <v>661</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>395</v>
+        <v>660</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>214</v>
+        <v>335</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>413</v>
+        <v>660</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>592</v>
+        <v>662</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>395</v>
+        <v>546</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>215</v>
+        <v>336</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>415</v>
+        <v>546</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>593</v>
+        <v>663</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>395</v>
+        <v>507</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>216</v>
+        <v>337</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>415</v>
+        <v>507</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>594</v>
+        <v>664</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>395</v>
+        <v>509</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>595</v>
+        <v>338</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>596</v>
+        <v>509</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>368</v>
+        <v>396</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>597</v>
+        <v>665</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>395</v>
+        <v>476</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>217</v>
+        <v>339</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>418</v>
+        <v>476</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>369</v>
+        <v>397</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>598</v>
+        <v>666</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>395</v>
+        <v>501</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>218</v>
+        <v>340</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>408</v>
+        <v>501</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>370</v>
+        <v>398</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>599</v>
+        <v>667</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>395</v>
+        <v>507</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>219</v>
+        <v>341</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>424</v>
+        <v>507</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>600</v>
+        <v>668</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>395</v>
+        <v>474</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>601</v>
+        <v>281</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>400</v>
+        <v>474</v>
       </c>
     </row>
     <row r="168" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>602</v>
+        <v>669</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>395</v>
+        <v>541</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>220</v>
+        <v>342</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>428</v>
+        <v>541</v>
       </c>
     </row>
     <row r="169" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>373</v>
+        <v>401</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>603</v>
+        <v>670</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>395</v>
+        <v>531</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>221</v>
+        <v>343</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>403</v>
+        <v>531</v>
       </c>
     </row>
     <row r="170" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>604</v>
+        <v>671</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>395</v>
+        <v>531</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>199</v>
+        <v>343</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>435</v>
+        <v>531</v>
       </c>
     </row>
     <row r="171" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>605</v>
+        <v>672</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>395</v>
+        <v>546</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>606</v>
+        <v>344</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>574</v>
+        <v>546</v>
       </c>
     </row>
     <row r="172" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>607</v>
+        <v>673</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>222</v>
+        <v>345</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>440</v>
+        <v>467</v>
       </c>
     </row>
     <row r="173" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>377</v>
+        <v>405</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>608</v>
+        <v>674</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>223</v>
+        <v>346</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>400</v>
+        <v>467</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>378</v>
+        <v>406</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>609</v>
+        <v>675</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>395</v>
+        <v>467</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>610</v>
+        <v>347</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>611</v>
+        <v>467</v>
       </c>
     </row>
     <row r="175" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>612</v>
+        <v>676</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>395</v>
+        <v>465</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>613</v>
+        <v>465</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>380</v>
+        <v>408</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>614</v>
+        <v>677</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>395</v>
+        <v>517</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>225</v>
+        <v>260</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>400</v>
+        <v>517</v>
       </c>
     </row>
     <row r="177" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>615</v>
+        <v>678</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>395</v>
+        <v>465</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>226</v>
+        <v>261</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>408</v>
+        <v>465</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>616</v>
+        <v>679</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>395</v>
+        <v>484</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>383</v>
+        <v>411</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>617</v>
+        <v>680</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>395</v>
+        <v>517</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>397</v>
+        <v>517</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>618</v>
+        <v>681</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>395</v>
+        <v>484</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>229</v>
+        <v>263</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>415</v>
+        <v>484</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>619</v>
+        <v>682</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>585</v>
+        <v>461</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>620</v>
+        <v>683</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>395</v>
+        <v>472</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>395</v>
+        <v>472</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E187" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E188" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E189" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E190" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E192" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E193" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E194" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E195" s="3" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E196" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E197" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B198" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E198" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B199" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="E199" s="3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B200" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E201" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B202" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B208" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B209" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B210" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="E210" s="3" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B211" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B212" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E212" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E213" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E214" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E215" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E216" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E217" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E218" s="3" t="s">
+        <v>459</v>
       </c>
     </row>
   </sheetData>
